--- a/patient_registration_form_templates/036_patient_assessment_form--patient_registration_form_templates.xlsx
+++ b/patient_registration_form_templates/036_patient_assessment_form--patient_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -830,8 +830,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -859,12 +859,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'mild'}</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Mild'}</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'headache'}</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Headache'}</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cough'}</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Cough'}</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'physical_therapy'}</t>
+          <t>physical_therapy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Physical Therapy'}</t>
+          <t>Physical Therapy</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medication'}</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medication'}</t>
+          <t>Medication</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'surgery'}</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Surgery'}</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
